--- a/IBKR-zakelijk-waarderen.xlsx
+++ b/IBKR-zakelijk-waarderen.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5FD70E-B7A5-4D1E-B057-1FAEE3C18E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{AD5FD70E-B7A5-4D1E-B057-1FAEE3C18E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A7D275B-FFD2-43D1-9D9D-CC01BD7F11A4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{010CA26D-E0A1-4330-9BB0-2FFE8661F74D}"/>
   </bookViews>
